--- a/dados/Rentabilizacao_dados.xlsx
+++ b/dados/Rentabilizacao_dados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cagliariparti-my.sharepoint.com/personal/kgguimaraes_verointernet_com_br/Documents/Área de Trabalho/Arquivos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cagliariparti-my.sharepoint.com/personal/kgguimaraes_verointernet_com_br/Documents/Área de Trabalho/Arquivos/vero-cards/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{4C8043C8-6B83-47F3-B2B8-D6C08AC3F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6767DA3-E935-46D7-8597-81E441F227B5}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{4C8043C8-6B83-47F3-B2B8-D6C08AC3F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D213B82-FF61-4ADF-8B8F-C9443616419F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{79388C02-44B3-4826-82E8-A0001CEF9978}"/>
   </bookViews>
@@ -1389,7 +1389,7 @@
   <dimension ref="B1:M14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
@@ -1450,36 +1450,24 @@
       <c r="D2" s="10">
         <v>80000</v>
       </c>
-      <c r="E2" s="10">
-        <v>2085288</v>
-      </c>
-      <c r="F2" s="12">
-        <f>E2/D2</f>
-        <v>26.066099999999999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6675</v>
-      </c>
-      <c r="H2" s="12">
-        <v>5368.856022243448</v>
-      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="10">
         <v>1306</v>
       </c>
-      <c r="J2" s="13">
-        <f>I2/G2</f>
-        <v>0.19565543071161048</v>
-      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="14">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="L2" s="14">
         <f>K2*22.5</f>
-        <v>1282.5</v>
+        <v>1642.5</v>
       </c>
       <c r="M2" s="15">
         <f>L2/D2</f>
-        <v>1.603125E-2</v>
+        <v>2.0531250000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1492,36 +1480,24 @@
       <c r="D3" s="10">
         <v>120000</v>
       </c>
-      <c r="E3" s="10">
-        <v>1582000</v>
-      </c>
-      <c r="F3" s="12">
-        <f t="shared" ref="F3:F4" si="0">E3/D3</f>
-        <v>13.183333333333334</v>
-      </c>
-      <c r="G3" s="10">
-        <f>SUM(H3,I3)</f>
-        <v>155587</v>
-      </c>
-      <c r="H3" s="10">
-        <v>152000</v>
-      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="10">
-        <v>3587</v>
-      </c>
-      <c r="J3" s="13">
-        <f>I3/G3</f>
-        <v>2.305462538643974E-2</v>
-      </c>
+        <f>K3*22.5</f>
+        <v>4365</v>
+      </c>
+      <c r="J3" s="13"/>
       <c r="K3" s="14">
         <v>194</v>
       </c>
       <c r="L3" s="14">
-        <f t="shared" ref="L3:L4" si="1">K3*22.5</f>
+        <f t="shared" ref="L3:L4" si="0">K3*22.5</f>
         <v>4365</v>
       </c>
       <c r="M3" s="15">
-        <f t="shared" ref="M3:M4" si="2">L3/D3</f>
+        <f t="shared" ref="M3:M4" si="1">L3/D3</f>
         <v>3.6374999999999998E-2</v>
       </c>
     </row>
@@ -1532,40 +1508,24 @@
       <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="10">
-        <v>60000</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1940</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" si="0"/>
-        <v>3.2333333333333332E-2</v>
-      </c>
-      <c r="G4" s="10">
-        <v>110</v>
-      </c>
-      <c r="H4" s="10">
-        <f>G4-I4</f>
-        <v>97</v>
-      </c>
-      <c r="I4" s="10">
-        <v>13</v>
-      </c>
-      <c r="J4" s="13">
-        <f>I4/G4</f>
-        <v>0.11818181818181818</v>
-      </c>
-      <c r="K4" s="14">
-        <v>2</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M4" s="15">
-        <f t="shared" si="2"/>
-        <v>7.5000000000000002E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -1662,7 +1622,7 @@
         <v>1582000</v>
       </c>
       <c r="F8" s="12">
-        <f t="shared" ref="F8:F9" si="3">E8/D8</f>
+        <f t="shared" ref="F8:F9" si="2">E8/D8</f>
         <v>13.183333333333334</v>
       </c>
       <c r="G8" s="10">
@@ -1683,11 +1643,11 @@
         <v>194</v>
       </c>
       <c r="L8" s="14">
-        <f t="shared" ref="L8:L9" si="4">K8*22.5</f>
+        <f t="shared" ref="L8:L9" si="3">K8*22.5</f>
         <v>4365</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" ref="M8:M9" si="5">L8/D8</f>
+        <f t="shared" ref="M8:M9" si="4">L8/D8</f>
         <v>3.6374999999999998E-2</v>
       </c>
     </row>
@@ -1705,7 +1665,7 @@
         <v>1940</v>
       </c>
       <c r="F9" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2333333333333332E-2</v>
       </c>
       <c r="G9" s="10">
@@ -1726,11 +1686,11 @@
         <v>2</v>
       </c>
       <c r="L9" s="14">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="M9" s="15">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="M9" s="15">
-        <f t="shared" si="5"/>
         <v>7.5000000000000002E-4</v>
       </c>
     </row>
@@ -1822,11 +1782,11 @@
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14">
-        <f t="shared" ref="L13:L14" si="6">K13*22.5</f>
+        <f t="shared" ref="L13:L14" si="5">K13*22.5</f>
         <v>0</v>
       </c>
       <c r="M13" s="15">
-        <f t="shared" ref="M13:M14" si="7">L13/D13</f>
+        <f t="shared" ref="M13:M14" si="6">L13/D13</f>
         <v>0</v>
       </c>
     </row>
@@ -1851,11 +1811,11 @@
       </c>
       <c r="K14" s="14"/>
       <c r="L14" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
